--- a/public/samples/pt-BR/sample2.xlsx
+++ b/public/samples/pt-BR/sample2.xlsx
@@ -35,7 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -77,10 +79,11 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +502,7 @@
       <c r="C3" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>7.2</v>
       </c>
       <c r="E3" s="2" t="str">
@@ -519,8 +522,8 @@
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D4" s="2" t="str">
-        <v>7.0</v>
+      <c r="D4" s="3">
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="str">
         <v/>
@@ -539,7 +542,7 @@
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>5.9</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -559,7 +562,7 @@
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>7.8</v>
       </c>
       <c r="E6" s="2" t="str">
@@ -579,7 +582,7 @@
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>7.4</v>
       </c>
       <c r="E7" s="2" t="str">
@@ -599,7 +602,7 @@
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>6.7</v>
       </c>
       <c r="E8" s="2" t="str">
@@ -619,7 +622,7 @@
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>5.9</v>
       </c>
       <c r="E9" s="2" t="str">
@@ -639,8 +642,8 @@
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D10" s="2" t="str">
-        <v>8.0</v>
+      <c r="D10" s="3">
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="str">
         <v/>
@@ -659,7 +662,7 @@
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>8.5</v>
       </c>
       <c r="E11" s="2" t="str">
@@ -679,7 +682,7 @@
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>7.7</v>
       </c>
       <c r="E12" s="2" t="str">
@@ -699,7 +702,7 @@
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>7.6</v>
       </c>
       <c r="E13" s="2" t="str">
@@ -719,7 +722,7 @@
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>8.2</v>
       </c>
       <c r="E14" s="2" t="str">
@@ -739,7 +742,7 @@
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>5.8</v>
       </c>
       <c r="E15" s="2" t="str">
@@ -759,8 +762,8 @@
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D16" s="2" t="str">
-        <v>8.0</v>
+      <c r="D16" s="3">
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="str">
         <v/>
@@ -779,7 +782,7 @@
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>7.8</v>
       </c>
       <c r="E17" s="2" t="str">
@@ -799,7 +802,7 @@
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>8.1</v>
       </c>
       <c r="E18" s="2" t="str">
@@ -819,7 +822,7 @@
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>8.5</v>
       </c>
       <c r="E19" s="2" t="str">
@@ -839,7 +842,7 @@
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>6.8</v>
       </c>
       <c r="E20" s="2" t="str">
@@ -859,7 +862,7 @@
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>6.4</v>
       </c>
       <c r="E21" s="2" t="str">
@@ -879,7 +882,7 @@
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>9.4</v>
       </c>
       <c r="E22" s="2" t="str">
@@ -899,7 +902,7 @@
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>8.4</v>
       </c>
       <c r="E23" s="2" t="str">
@@ -919,7 +922,7 @@
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>6.6</v>
       </c>
       <c r="E24" s="2" t="str">
@@ -939,7 +942,7 @@
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>7.4</v>
       </c>
       <c r="E25" s="2" t="str">
@@ -959,7 +962,7 @@
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>6.5</v>
       </c>
       <c r="E26" s="2" t="str">
@@ -979,7 +982,7 @@
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>6.9</v>
       </c>
       <c r="E27" s="2" t="str">
@@ -999,7 +1002,7 @@
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>9.4</v>
       </c>
       <c r="E28" s="2" t="str">
@@ -1019,7 +1022,7 @@
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>8.1</v>
       </c>
       <c r="E29" s="2" t="str">
@@ -1039,7 +1042,7 @@
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>5.9</v>
       </c>
       <c r="E30" s="2" t="str">
@@ -1059,7 +1062,7 @@
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <v>8.5</v>
       </c>
       <c r="E31" s="2" t="str">
@@ -1079,7 +1082,7 @@
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
         <v>6.2</v>
       </c>
       <c r="E32" s="2" t="str">
@@ -1099,8 +1102,8 @@
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D33" s="2" t="str">
-        <v>8.0</v>
+      <c r="D33" s="3">
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="str">
         <v/>
@@ -1119,7 +1122,7 @@
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
         <v>7.6</v>
       </c>
       <c r="E34" s="2" t="str">
@@ -1139,7 +1142,7 @@
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="3">
         <v>8.2</v>
       </c>
       <c r="E35" s="2" t="str">
@@ -1159,7 +1162,7 @@
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="3">
         <v>7.4</v>
       </c>
       <c r="E36" s="2" t="str">
@@ -1179,7 +1182,7 @@
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
         <v>8.3</v>
       </c>
       <c r="E37" s="2" t="str">
@@ -1199,7 +1202,7 @@
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="3">
         <v>7.8</v>
       </c>
       <c r="E38" s="2" t="str">
@@ -1219,7 +1222,7 @@
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
         <v>7.3</v>
       </c>
       <c r="E39" s="2" t="str">
@@ -1239,8 +1242,8 @@
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D40" s="2" t="str">
-        <v>7.0</v>
+      <c r="D40" s="3">
+        <v>7</v>
       </c>
       <c r="E40" s="2" t="str">
         <v/>
@@ -1259,7 +1262,7 @@
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
         <v>7.6</v>
       </c>
       <c r="E41" s="2" t="str">
@@ -1279,7 +1282,7 @@
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>9.2</v>
       </c>
       <c r="E42" s="2" t="str">
@@ -1299,7 +1302,7 @@
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
         <v>7.3</v>
       </c>
       <c r="E43" s="2" t="str">
@@ -1319,7 +1322,7 @@
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>6.8</v>
       </c>
       <c r="E44" s="2" t="str">
@@ -1339,7 +1342,7 @@
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <v>7.5</v>
       </c>
       <c r="E45" s="2" t="str">
@@ -1359,7 +1362,7 @@
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="3">
         <v>6.1</v>
       </c>
       <c r="E46" s="2" t="str">
@@ -1379,7 +1382,7 @@
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <v>7.6</v>
       </c>
       <c r="E47" s="2" t="str">
@@ -1399,7 +1402,7 @@
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
         <v>5.5</v>
       </c>
       <c r="E48" s="2" t="str">
@@ -1419,7 +1422,7 @@
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <v>6.8</v>
       </c>
       <c r="E49" s="2" t="str">
@@ -1439,7 +1442,7 @@
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="3">
         <v>6.4</v>
       </c>
       <c r="E50" s="2" t="str">
@@ -1459,7 +1462,7 @@
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
         <v>7.5</v>
       </c>
       <c r="E51" s="2" t="str">
@@ -1479,7 +1482,7 @@
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
         <v>7.2</v>
       </c>
       <c r="E52" s="2" t="str">
@@ -1499,8 +1502,8 @@
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D53" s="2" t="str">
-        <v>7.0</v>
+      <c r="D53" s="3">
+        <v>7</v>
       </c>
       <c r="E53" s="2" t="str">
         <v/>
@@ -1519,7 +1522,7 @@
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="3">
         <v>6.2</v>
       </c>
       <c r="E54" s="2" t="str">
@@ -1539,7 +1542,7 @@
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="3">
         <v>7.4</v>
       </c>
       <c r="E55" s="2" t="str">
@@ -1559,7 +1562,7 @@
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="3">
         <v>7.8</v>
       </c>
       <c r="E56" s="2" t="str">
@@ -1579,7 +1582,7 @@
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="3">
         <v>8.6</v>
       </c>
       <c r="E57" s="2" t="str">
@@ -1599,7 +1602,7 @@
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="3">
         <v>6.2</v>
       </c>
       <c r="E58" s="2" t="str">
@@ -1619,7 +1622,7 @@
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="3">
         <v>7.7</v>
       </c>
       <c r="E59" s="2" t="str">
@@ -1639,7 +1642,7 @@
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="3">
         <v>8.1</v>
       </c>
       <c r="E60" s="2" t="str">
@@ -1659,7 +1662,7 @@
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="3">
         <v>8.6</v>
       </c>
       <c r="E61" s="2" t="str">
@@ -1679,7 +1682,7 @@
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="3">
         <v>6.2</v>
       </c>
       <c r="E62" s="2" t="str">
@@ -1699,7 +1702,7 @@
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="3">
         <v>6.2</v>
       </c>
       <c r="E63" s="2" t="str">
@@ -1719,7 +1722,7 @@
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="3">
         <v>7.7</v>
       </c>
       <c r="E64" s="2" t="str">
@@ -1739,7 +1742,7 @@
       <c r="C65" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="3">
         <v>6.3</v>
       </c>
       <c r="E65" s="2" t="str">
@@ -1759,7 +1762,7 @@
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="3">
         <v>7.9</v>
       </c>
       <c r="E66" s="2" t="str">
@@ -1774,12 +1777,12 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Beatriz Souza</v>
+        <v>Luiza Souza</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="3">
         <v>6.6</v>
       </c>
       <c r="E67" s="2" t="str">
@@ -1794,13 +1797,13 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Matheus Fernandes</v>
+        <v>Matheus Gomes</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D68" s="2">
-        <v>7.7</v>
+      <c r="D68" s="3">
+        <v>8.3</v>
       </c>
       <c r="E68" s="2" t="str">
         <v/>
@@ -1814,13 +1817,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Luiza Oliveira</v>
+        <v>Lorena Santos</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D69" s="2">
-        <v>7.5</v>
+      <c r="D69" s="3">
+        <v>6.9</v>
       </c>
       <c r="E69" s="2" t="str">
         <v/>
@@ -1834,19 +1837,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Benício Costa</v>
+        <v>Benício Alves</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D70" s="2">
-        <v>6.7</v>
+      <c r="D70" s="3">
+        <v>6.9</v>
       </c>
       <c r="E70" s="2" t="str">
         <v/>
       </c>
       <c r="F70" s="2" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="71">
@@ -1854,19 +1857,19 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Lorena Soares</v>
+        <v>Giovanna Barbosa</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D71" s="2">
-        <v>5.9</v>
+      <c r="D71" s="3">
+        <v>6.1</v>
       </c>
       <c r="E71" s="2" t="str">
         <v/>
       </c>
       <c r="F71" s="2" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="72">
@@ -1874,19 +1877,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Nicolas Pereira</v>
+        <v>Nicolas Soares</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D72" s="2">
-        <v>8.8</v>
+      <c r="D72" s="3">
+        <v>8</v>
       </c>
       <c r="E72" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="73">
@@ -1894,13 +1897,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Giovanna Rodrigues</v>
+        <v>Mariana Fernandes</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D73" s="2">
-        <v>7.9</v>
+      <c r="D73" s="3">
+        <v>7.4</v>
       </c>
       <c r="E73" s="2" t="str">
         <v/>
@@ -1914,19 +1917,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Gustavo Martins</v>
+        <v>Gustavo Alves</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D74" s="2">
-        <v>9.1</v>
+      <c r="D74" s="3">
+        <v>8.5</v>
       </c>
       <c r="E74" s="2" t="str">
         <v/>
       </c>
       <c r="F74" s="2" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="75">
@@ -1934,19 +1937,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Mariana Costa</v>
+        <v>Antonella Almeida</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D75" s="2">
-        <v>7.5</v>
+      <c r="D75" s="3">
+        <v>8</v>
       </c>
       <c r="E75" s="2" t="str">
         <v/>
       </c>
       <c r="F75" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="76">
@@ -1954,19 +1957,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Guilherme Silva</v>
+        <v>Guilherme Barbosa</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D76" s="2">
-        <v>8.4</v>
+      <c r="D76" s="3">
+        <v>7.9</v>
       </c>
       <c r="E76" s="2" t="str">
         <v/>
       </c>
       <c r="F76" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="77">
@@ -1974,19 +1977,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Antonella Fernandes</v>
+        <v>Clara Barbosa</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D77" s="2">
-        <v>8.8</v>
+      <c r="D77" s="3">
+        <v>7.6</v>
       </c>
       <c r="E77" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F77" s="2" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="78">
@@ -1994,19 +1997,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Joaquim Silva</v>
+        <v>Miguel Soares</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D78" s="2">
-        <v>8.5</v>
+      <c r="D78" s="3">
+        <v>7.5</v>
       </c>
       <c r="E78" s="2" t="str">
         <v/>
       </c>
       <c r="F78" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="79">
@@ -2014,19 +2017,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Helena Almeida</v>
+        <v>Helena Barbosa</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D79" s="2">
-        <v>7.6</v>
+      <c r="D79" s="3">
+        <v>8.8</v>
       </c>
       <c r="E79" s="2" t="str">
         <v/>
       </c>
       <c r="F79" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="80">
@@ -2034,19 +2037,19 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Miguel Soares</v>
+        <v>Arthur Lima</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D80" s="2">
-        <v>8.3</v>
+      <c r="D80" s="3">
+        <v>7.4</v>
       </c>
       <c r="E80" s="2" t="str">
         <v/>
       </c>
       <c r="F80" s="2" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="81">
@@ -2054,13 +2057,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Alice Santos</v>
+        <v>Alice Alves</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D81" s="2">
-        <v>8.3</v>
+      <c r="D81" s="3">
+        <v>7.8</v>
       </c>
       <c r="E81" s="2" t="str">
         <v/>
@@ -2074,19 +2077,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Arthur Alves</v>
+        <v>Gael Almeida</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D82" s="2">
-        <v>5.7</v>
+      <c r="D82" s="3">
+        <v>5.6</v>
       </c>
       <c r="E82" s="2" t="str">
         <v/>
       </c>
       <c r="F82" s="2" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
   </sheetData>
@@ -2102,13 +2105,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="C1" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2124,21 +2127,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/pt-BR/sample2.xlsx
+++ b/public/samples/pt-BR/sample2.xlsx
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -471,6 +471,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -486,9 +489,12 @@
         <v>Média</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>AEE</v>
+        <v>Nível de matemática</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>Apoio educacional</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>Turma de origem</v>
       </c>
     </row>
@@ -497,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>Helena Lopes</v>
+        <v>Helena Rodrigues</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>F</v>
@@ -505,11 +511,14 @@
       <c r="D3" s="3">
         <v>7.2</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="4">
@@ -517,19 +526,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Miguel Oliveira</v>
+        <v>Miguel Silva</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D4" s="3">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="5">
@@ -537,19 +549,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Alice Lopes</v>
+        <v>Alice Pereira</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D5" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v>✓</v>
+        <v>6.3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="6">
@@ -557,19 +572,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>Arthur Vieira</v>
+        <v>Arthur Barbosa</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D6" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="7">
@@ -577,18 +595,21 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Laura Rodrigues</v>
+        <v>Laura Oliveira</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D7" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>6.5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -597,18 +618,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Gael Alves</v>
+        <v>Gael Vieira</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D8" s="3">
-        <v>6.7</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>6.2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -617,18 +641,21 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Maria Alice Vieira</v>
+        <v>Maria Alice Lopes</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D9" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -637,19 +664,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Heitor Rodrigues</v>
+        <v>Heitor Silva</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D10" s="3">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+        <v>8.6</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +687,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Valentina Costa</v>
+        <v>Valentina Ribeiro</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D11" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="12">
@@ -677,19 +710,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>Theo Martins</v>
+        <v>Theo Silva</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D12" s="3">
-        <v>7.7</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +733,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Heloísa Silva</v>
+        <v>Heloísa Barbosa</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D13" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>6.3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="14">
@@ -717,18 +756,21 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Davi Rodrigues</v>
+        <v>Davi Santos</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D14" s="3">
-        <v>8.2</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v>✓</v>
+        <v>6.8</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -737,18 +779,21 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Maria Clara Oliveira</v>
+        <v>Maria Clara Lopes</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D15" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -757,19 +802,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Gabriel Santos</v>
+        <v>Gabriel Soares</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D16" s="3">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="17">
@@ -777,19 +825,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Cecília Vieira</v>
+        <v>Cecília Costa</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D17" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+        <v>9.1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="18">
@@ -797,18 +848,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Bernardo Martins</v>
+        <v>Bernardo Barbosa</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>6.6</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -817,19 +871,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Júlia Oliveira</v>
+        <v>Júlia Martins</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D19" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="20">
@@ -837,19 +894,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Samuel Rodrigues</v>
+        <v>Samuel Ribeiro</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>8.4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="21">
@@ -857,18 +917,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Sophia Martins</v>
+        <v>Sophia Almeida</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D21" s="3">
-        <v>6.4</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+        <v>6.6</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -877,19 +940,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>João Miguel Almeida</v>
+        <v>João Miguel Oliveira</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="23">
@@ -897,19 +963,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Manuela Ribeiro</v>
+        <v>Manuela Souza</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D23" s="3">
-        <v>8.4</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="24">
@@ -917,18 +986,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Pedro Alves</v>
+        <v>Pedro Barbosa</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+        <v>8.2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -937,18 +1009,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Isabela Fernandes</v>
+        <v>Isabela Almeida</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>8.9</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -957,19 +1032,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Lucas Silva</v>
+        <v>Lucas Gomes</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D26" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G26" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="27">
@@ -977,18 +1055,21 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Lívia Lima</v>
+        <v>Lívia Oliveira</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D27" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+        <v>8.5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4</v>
       </c>
       <c r="F27" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1003,13 +1084,16 @@
         <v>M</v>
       </c>
       <c r="D28" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>6.6</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="29">
@@ -1017,19 +1101,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Beatriz Oliveira</v>
+        <v>Beatriz Lima</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>6.3</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="30">
@@ -1037,19 +1124,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Enzo Gomes</v>
+        <v>Enzo Almeida</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D30" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v>✓</v>
+        <v>6.5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="31">
@@ -1057,19 +1147,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Luiza Ribeiro</v>
+        <v>Luiza Costa</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+        <v>6.1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
       </c>
       <c r="F31" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="32">
@@ -1077,18 +1170,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Matheus Oliveira</v>
+        <v>Matheus Vieira</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>8.5</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1103,12 +1199,15 @@
         <v>F</v>
       </c>
       <c r="D33" s="3">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2</v>
       </c>
       <c r="F33" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1117,19 +1216,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Benício Oliveira</v>
+        <v>Benício Alves</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D34" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="35">
@@ -1137,19 +1239,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Giovanna Oliveira</v>
+        <v>Giovanna Souza</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D35" s="3">
-        <v>8.2</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>7.3</v>
+      </c>
+      <c r="E35" s="2">
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="36">
@@ -1157,19 +1262,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Nicolas Lima</v>
+        <v>Nicolas Alves</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D36" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>7.2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>4</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="37">
@@ -1177,18 +1285,21 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Mariana Vieira</v>
+        <v>Mariana Fernandes</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D37" s="3">
-        <v>8.3</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>7.7</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2</v>
       </c>
       <c r="F37" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1197,19 +1308,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>Gustavo Souza</v>
+        <v>Gustavo Carvalho</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D38" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+        <v>6.3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="39">
@@ -1217,19 +1331,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Antonella Costa</v>
+        <v>Antonella Gomes</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D39" s="3">
-        <v>7.3</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3</v>
       </c>
       <c r="F39" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="40">
@@ -1237,19 +1354,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>Guilherme Costa</v>
+        <v>Guilherme Barbosa</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D40" s="3">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>6.8</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="41">
@@ -1257,19 +1377,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Clara Martins</v>
+        <v>Clara Silva</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D41" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v>✓</v>
+        <v>8.5</v>
+      </c>
+      <c r="E41" s="2">
+        <v>4</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="42">
@@ -1277,19 +1400,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Joaquim Souza</v>
+        <v>Joaquim Costa</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D42" s="3">
-        <v>9.2</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>7.4</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="43">
@@ -1297,19 +1423,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>Helena Souza</v>
+        <v>Helena Carvalho</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D43" s="3">
-        <v>7.3</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>7.1</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
       </c>
       <c r="F43" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="44">
@@ -1317,19 +1446,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Miguel Carvalho</v>
+        <v>Miguel Costa</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D44" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="45">
@@ -1337,19 +1469,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Alice Soares</v>
+        <v>Alice Martins</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D45" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>6.2</v>
+      </c>
+      <c r="E45" s="2">
+        <v>4</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="46">
@@ -1357,19 +1492,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Arthur Soares</v>
+        <v>Arthur Gomes</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D46" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>8.1</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="47">
@@ -1383,13 +1521,16 @@
         <v>F</v>
       </c>
       <c r="D47" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+        <v>6.2</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="48">
@@ -1397,19 +1538,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Gael Soares</v>
+        <v>Heitor Ribeiro</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D48" s="3">
-        <v>5.5</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>6.9</v>
+      </c>
+      <c r="E48" s="2">
+        <v>5</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="49">
@@ -1417,19 +1561,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Maria Alice Lopes</v>
+        <v>Maria Alice Carvalho</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D49" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>8.8</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2</v>
       </c>
       <c r="F49" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="50">
@@ -1437,18 +1584,21 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Heitor Souza</v>
+        <v>Theo Fernandes</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D50" s="3">
-        <v>6.4</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v>✓</v>
+        <v>6.3</v>
+      </c>
+      <c r="E50" s="2">
+        <v>3</v>
       </c>
       <c r="F50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1457,19 +1607,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Heloísa Oliveira</v>
+        <v>Valentina Ferreira</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D51" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>6.5</v>
+      </c>
+      <c r="E51" s="2">
+        <v>4</v>
       </c>
       <c r="F51" s="2" t="str">
-        <v>A</v>
+        <v>✓</v>
+      </c>
+      <c r="G51" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="52">
@@ -1477,19 +1630,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Davi Almeida</v>
+        <v>Davi Carvalho</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D52" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>8.1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>A</v>
+        <v>✓</v>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="53">
@@ -1497,19 +1653,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Maria Clara Gomes</v>
+        <v>Heloísa Gomes</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D53" s="3">
-        <v>7</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>8.5</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="54">
@@ -1517,19 +1676,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Gabriel Lima</v>
+        <v>Gabriel Santos</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D54" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2</v>
       </c>
       <c r="F54" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="55">
@@ -1537,19 +1699,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Cecília Carvalho</v>
+        <v>Maria Clara Rodrigues</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D55" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>6.8</v>
+      </c>
+      <c r="E55" s="2">
+        <v>2</v>
       </c>
       <c r="F55" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="56">
@@ -1557,19 +1722,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Bernardo Fernandes</v>
+        <v>Bernardo Oliveira</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D56" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="E56" s="2">
+        <v>2</v>
       </c>
       <c r="F56" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="57">
@@ -1577,19 +1745,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Júlia Ferreira</v>
+        <v>Cecília Martins</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D57" s="3">
-        <v>8.6</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>8.2</v>
+      </c>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="58">
@@ -1597,19 +1768,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Samuel Santos</v>
+        <v>Samuel Souza</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D58" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>6.7</v>
+      </c>
+      <c r="E58" s="2">
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="59">
@@ -1617,7 +1791,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Sophia Ferreira</v>
+        <v>Júlia Gomes</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>F</v>
@@ -1625,11 +1799,14 @@
       <c r="D59" s="3">
         <v>7.7</v>
       </c>
-      <c r="E59" s="2" t="str">
-        <v>✓</v>
+      <c r="E59" s="2">
+        <v>3</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="60">
@@ -1637,18 +1814,21 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>João Miguel Vieira</v>
+        <v>João Miguel Almeida</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D60" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>6.9</v>
+      </c>
+      <c r="E60" s="2">
+        <v>2</v>
       </c>
       <c r="F60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1657,19 +1837,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Manuela Santos</v>
+        <v>Sophia Souza</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D61" s="3">
-        <v>8.6</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E61" s="2">
+        <v>3</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="62">
@@ -1677,18 +1860,21 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Lucas Soares</v>
+        <v>Pedro Costa</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D62" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E62" s="2">
+        <v>5</v>
       </c>
       <c r="F62" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1697,19 +1883,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Isabela Alves</v>
+        <v>Isabela Rodrigues</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D63" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E63" s="2">
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="64">
@@ -1717,19 +1906,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Rafael Barbosa</v>
+        <v>Lucas Alves</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D64" s="3">
-        <v>7.7</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+        <v>9.1</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G64" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="65">
@@ -1743,12 +1935,15 @@
         <v>F</v>
       </c>
       <c r="D65" s="3">
-        <v>6.3</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="E65" s="2">
+        <v>5</v>
       </c>
       <c r="F65" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1757,18 +1952,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Enzo Lima</v>
+        <v>Rafael Carvalho</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D66" s="3">
-        <v>7.9</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+        <v>7.4</v>
+      </c>
+      <c r="E66" s="2">
+        <v>1</v>
       </c>
       <c r="F66" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G66" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1777,19 +1975,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Luiza Souza</v>
+        <v>Beatriz Pereira</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D67" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E67" s="2">
+        <v>5</v>
       </c>
       <c r="F67" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G67" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="68">
@@ -1797,19 +1998,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Matheus Gomes</v>
+        <v>Enzo Barbosa</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D68" s="3">
-        <v>8.3</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>6.4</v>
+      </c>
+      <c r="E68" s="2">
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G68" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="69">
@@ -1817,19 +2021,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Lorena Santos</v>
+        <v>Luiza Martins</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D69" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="E69" s="2">
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G69" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="70">
@@ -1837,19 +2044,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Benício Alves</v>
+        <v>Matheus Santos</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D70" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+        <v>8.5</v>
+      </c>
+      <c r="E70" s="2">
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G70" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="71">
@@ -1857,19 +2067,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Giovanna Barbosa</v>
+        <v>Lorena Almeida</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D71" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E71" s="2">
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G71" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="72">
@@ -1877,19 +2090,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Nicolas Soares</v>
+        <v>Benício Martins</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D72" s="3">
-        <v>8</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v>✓</v>
+        <v>7.7</v>
+      </c>
+      <c r="E72" s="2">
+        <v>3</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G72" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="73">
@@ -1897,19 +2113,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Mariana Fernandes</v>
+        <v>Giovanna Santos</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D73" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+        <v>7.6</v>
+      </c>
+      <c r="E73" s="2">
+        <v>5</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G73" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="74">
@@ -1917,18 +2136,21 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Gustavo Alves</v>
+        <v>Nicolas Costa</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D74" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+        <v>7.3</v>
+      </c>
+      <c r="E74" s="2">
+        <v>5</v>
       </c>
       <c r="F74" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1937,19 +2159,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Antonella Almeida</v>
+        <v>Mariana Oliveira</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D75" s="3">
-        <v>8</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E75" s="2">
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G75" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="76">
@@ -1957,19 +2182,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Guilherme Barbosa</v>
+        <v>Gustavo Gomes</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D76" s="3">
-        <v>7.9</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>7.6</v>
+      </c>
+      <c r="E76" s="2">
+        <v>4</v>
       </c>
       <c r="F76" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G76" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="77">
@@ -1977,18 +2205,21 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Clara Barbosa</v>
+        <v>Antonella Lopes</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D77" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v>✓</v>
+        <v>7.9</v>
+      </c>
+      <c r="E77" s="2">
+        <v>3</v>
       </c>
       <c r="F77" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G77" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1997,19 +2228,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Miguel Soares</v>
+        <v>Guilherme Vieira</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D78" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>8.7</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
       </c>
       <c r="F78" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G78" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="79">
@@ -2017,19 +2251,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Helena Barbosa</v>
+        <v>Clara Gomes</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D79" s="3">
-        <v>8.8</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>6.9</v>
+      </c>
+      <c r="E79" s="2">
+        <v>1</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G79" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="80">
@@ -2037,19 +2274,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Arthur Lima</v>
+        <v>Joaquim Santos</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D80" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="E80" s="2">
+        <v>3</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G80" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="81">
@@ -2057,19 +2297,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Alice Alves</v>
+        <v>Helena Almeida</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D81" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>6.1</v>
+      </c>
+      <c r="E81" s="2">
+        <v>3</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G81" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="82">
@@ -2077,24 +2320,27 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Gael Almeida</v>
+        <v>Miguel Almeida</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D82" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>7.7</v>
+      </c>
+      <c r="E82" s="2">
+        <v>5</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2105,13 +2351,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2127,21 +2373,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="B1" s="2">
-        <v>77</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/pt-BR/sample2.xlsx
+++ b/public/samples/pt-BR/sample2.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Lista de alunos" sheetId="2" r:id="rId2"/>
     <sheet name="Manter juntos" sheetId="3" r:id="rId3"/>
     <sheet name="Separar" sheetId="4" r:id="rId4"/>
+    <sheet name="Critérios" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -2395,4 +2396,84 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Critério</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Opções</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Gênero</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Média</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Número</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Nível de matemática</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Nível</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Apoio educacional</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Caixa de seleção</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Turma de origem</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/pt-BR/sample2.xlsx
+++ b/public/samples/pt-BR/sample2.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Lista de alunos" sheetId="2" r:id="rId2"/>
     <sheet name="Manter juntos" sheetId="3" r:id="rId3"/>
     <sheet name="Separar" sheetId="4" r:id="rId4"/>
+    <sheet name="Critérios" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -450,7 +451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -471,6 +472,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -486,9 +490,12 @@
         <v>Média</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>AEE</v>
+        <v>Nível de matemática</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>Apoio educacional</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>Turma de origem</v>
       </c>
     </row>
@@ -497,7 +504,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>Helena Lopes</v>
+        <v>Helena Rodrigues</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>F</v>
@@ -505,11 +512,14 @@
       <c r="D3" s="3">
         <v>7.2</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="4">
@@ -517,19 +527,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Miguel Oliveira</v>
+        <v>Miguel Silva</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D4" s="3">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="5">
@@ -537,19 +550,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Alice Lopes</v>
+        <v>Alice Pereira</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D5" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v>✓</v>
+        <v>6.3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="6">
@@ -557,19 +573,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>Arthur Vieira</v>
+        <v>Arthur Barbosa</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D6" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="7">
@@ -577,18 +596,21 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Laura Rodrigues</v>
+        <v>Laura Oliveira</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D7" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>6.5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -597,18 +619,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Gael Alves</v>
+        <v>Gael Vieira</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D8" s="3">
-        <v>6.7</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>6.2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -617,18 +642,21 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Maria Alice Vieira</v>
+        <v>Maria Alice Lopes</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D9" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -637,19 +665,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Heitor Rodrigues</v>
+        <v>Heitor Silva</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D10" s="3">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+        <v>8.6</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +688,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Valentina Costa</v>
+        <v>Valentina Ribeiro</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D11" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="12">
@@ -677,19 +711,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>Theo Martins</v>
+        <v>Theo Silva</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D12" s="3">
-        <v>7.7</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +734,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Heloísa Silva</v>
+        <v>Heloísa Barbosa</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D13" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>6.3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="14">
@@ -717,18 +757,21 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Davi Rodrigues</v>
+        <v>Davi Santos</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D14" s="3">
-        <v>8.2</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v>✓</v>
+        <v>6.8</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -737,18 +780,21 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Maria Clara Oliveira</v>
+        <v>Maria Clara Lopes</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D15" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -757,19 +803,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Gabriel Santos</v>
+        <v>Gabriel Soares</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D16" s="3">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="17">
@@ -777,19 +826,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Cecília Vieira</v>
+        <v>Cecília Costa</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D17" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+        <v>9.1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="18">
@@ -797,18 +849,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Bernardo Martins</v>
+        <v>Bernardo Barbosa</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>6.6</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -817,19 +872,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Júlia Oliveira</v>
+        <v>Júlia Martins</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D19" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="20">
@@ -837,19 +895,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Samuel Rodrigues</v>
+        <v>Samuel Ribeiro</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>8.4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="21">
@@ -857,18 +918,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Sophia Martins</v>
+        <v>Sophia Almeida</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D21" s="3">
-        <v>6.4</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+        <v>6.6</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -877,19 +941,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>João Miguel Almeida</v>
+        <v>João Miguel Oliveira</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="23">
@@ -897,19 +964,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Manuela Ribeiro</v>
+        <v>Manuela Souza</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D23" s="3">
-        <v>8.4</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="24">
@@ -917,18 +987,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Pedro Alves</v>
+        <v>Pedro Barbosa</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+        <v>8.2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -937,18 +1010,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Isabela Fernandes</v>
+        <v>Isabela Almeida</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>8.9</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -957,19 +1033,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Lucas Silva</v>
+        <v>Lucas Gomes</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D26" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G26" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="27">
@@ -977,18 +1056,21 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Lívia Lima</v>
+        <v>Lívia Oliveira</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D27" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+        <v>8.5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4</v>
       </c>
       <c r="F27" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1003,13 +1085,16 @@
         <v>M</v>
       </c>
       <c r="D28" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>6.6</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="29">
@@ -1017,19 +1102,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Beatriz Oliveira</v>
+        <v>Beatriz Lima</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>6.3</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="30">
@@ -1037,19 +1125,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Enzo Gomes</v>
+        <v>Enzo Almeida</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D30" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v>✓</v>
+        <v>6.5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="31">
@@ -1057,19 +1148,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Luiza Ribeiro</v>
+        <v>Luiza Costa</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+        <v>6.1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
       </c>
       <c r="F31" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="32">
@@ -1077,18 +1171,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Matheus Oliveira</v>
+        <v>Matheus Vieira</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>8.5</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1103,12 +1200,15 @@
         <v>F</v>
       </c>
       <c r="D33" s="3">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2</v>
       </c>
       <c r="F33" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1117,19 +1217,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Benício Oliveira</v>
+        <v>Benício Alves</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D34" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="35">
@@ -1137,19 +1240,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Giovanna Oliveira</v>
+        <v>Giovanna Souza</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D35" s="3">
-        <v>8.2</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>7.3</v>
+      </c>
+      <c r="E35" s="2">
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="36">
@@ -1157,19 +1263,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Nicolas Lima</v>
+        <v>Nicolas Alves</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D36" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>7.2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>4</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="37">
@@ -1177,18 +1286,21 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Mariana Vieira</v>
+        <v>Mariana Fernandes</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D37" s="3">
-        <v>8.3</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>7.7</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2</v>
       </c>
       <c r="F37" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1197,19 +1309,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>Gustavo Souza</v>
+        <v>Gustavo Carvalho</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D38" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+        <v>6.3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="39">
@@ -1217,19 +1332,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Antonella Costa</v>
+        <v>Antonella Gomes</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D39" s="3">
-        <v>7.3</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3</v>
       </c>
       <c r="F39" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="40">
@@ -1237,19 +1355,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>Guilherme Costa</v>
+        <v>Guilherme Barbosa</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D40" s="3">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>6.8</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="41">
@@ -1257,19 +1378,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Clara Martins</v>
+        <v>Clara Silva</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D41" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v>✓</v>
+        <v>8.5</v>
+      </c>
+      <c r="E41" s="2">
+        <v>4</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="42">
@@ -1277,19 +1401,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Joaquim Souza</v>
+        <v>Joaquim Costa</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D42" s="3">
-        <v>9.2</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>7.4</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="43">
@@ -1297,19 +1424,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>Helena Souza</v>
+        <v>Helena Carvalho</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D43" s="3">
-        <v>7.3</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>7.1</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
       </c>
       <c r="F43" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="44">
@@ -1317,19 +1447,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Miguel Carvalho</v>
+        <v>Miguel Costa</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D44" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+        <v>7.8</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="45">
@@ -1337,19 +1470,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Alice Soares</v>
+        <v>Alice Martins</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D45" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>6.2</v>
+      </c>
+      <c r="E45" s="2">
+        <v>4</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="46">
@@ -1357,19 +1493,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Arthur Soares</v>
+        <v>Arthur Gomes</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D46" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>8.1</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="47">
@@ -1383,13 +1522,16 @@
         <v>F</v>
       </c>
       <c r="D47" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+        <v>6.2</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="48">
@@ -1397,19 +1539,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Gael Soares</v>
+        <v>Heitor Ribeiro</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D48" s="3">
-        <v>5.5</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>6.9</v>
+      </c>
+      <c r="E48" s="2">
+        <v>5</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="49">
@@ -1417,19 +1562,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Maria Alice Lopes</v>
+        <v>Maria Alice Carvalho</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D49" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>8.8</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2</v>
       </c>
       <c r="F49" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="50">
@@ -1437,18 +1585,21 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Heitor Souza</v>
+        <v>Theo Fernandes</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D50" s="3">
-        <v>6.4</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v>✓</v>
+        <v>6.3</v>
+      </c>
+      <c r="E50" s="2">
+        <v>3</v>
       </c>
       <c r="F50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1457,19 +1608,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Heloísa Oliveira</v>
+        <v>Valentina Ferreira</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D51" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>6.5</v>
+      </c>
+      <c r="E51" s="2">
+        <v>4</v>
       </c>
       <c r="F51" s="2" t="str">
-        <v>A</v>
+        <v>✓</v>
+      </c>
+      <c r="G51" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="52">
@@ -1477,19 +1631,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Davi Almeida</v>
+        <v>Davi Carvalho</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D52" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>8.1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>A</v>
+        <v>✓</v>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="53">
@@ -1497,19 +1654,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Maria Clara Gomes</v>
+        <v>Heloísa Gomes</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D53" s="3">
-        <v>7</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>8.5</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="54">
@@ -1517,19 +1677,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Gabriel Lima</v>
+        <v>Gabriel Santos</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D54" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2</v>
       </c>
       <c r="F54" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="55">
@@ -1537,19 +1700,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Cecília Carvalho</v>
+        <v>Maria Clara Rodrigues</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D55" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>6.8</v>
+      </c>
+      <c r="E55" s="2">
+        <v>2</v>
       </c>
       <c r="F55" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="56">
@@ -1557,19 +1723,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Bernardo Fernandes</v>
+        <v>Bernardo Oliveira</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D56" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="E56" s="2">
+        <v>2</v>
       </c>
       <c r="F56" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="57">
@@ -1577,19 +1746,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Júlia Ferreira</v>
+        <v>Cecília Martins</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D57" s="3">
-        <v>8.6</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>8.2</v>
+      </c>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="58">
@@ -1597,19 +1769,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Samuel Santos</v>
+        <v>Samuel Souza</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D58" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>6.7</v>
+      </c>
+      <c r="E58" s="2">
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="59">
@@ -1617,7 +1792,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Sophia Ferreira</v>
+        <v>Júlia Gomes</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>F</v>
@@ -1625,11 +1800,14 @@
       <c r="D59" s="3">
         <v>7.7</v>
       </c>
-      <c r="E59" s="2" t="str">
-        <v>✓</v>
+      <c r="E59" s="2">
+        <v>3</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="60">
@@ -1637,18 +1815,21 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>João Miguel Vieira</v>
+        <v>João Miguel Almeida</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D60" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>6.9</v>
+      </c>
+      <c r="E60" s="2">
+        <v>2</v>
       </c>
       <c r="F60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1657,19 +1838,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Manuela Santos</v>
+        <v>Sophia Souza</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D61" s="3">
-        <v>8.6</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E61" s="2">
+        <v>3</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="62">
@@ -1677,18 +1861,21 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Lucas Soares</v>
+        <v>Pedro Costa</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D62" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="E62" s="2">
+        <v>5</v>
       </c>
       <c r="F62" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1697,19 +1884,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Isabela Alves</v>
+        <v>Isabela Rodrigues</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D63" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E63" s="2">
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="64">
@@ -1717,19 +1907,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Rafael Barbosa</v>
+        <v>Lucas Alves</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D64" s="3">
-        <v>7.7</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+        <v>9.1</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G64" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="65">
@@ -1743,12 +1936,15 @@
         <v>F</v>
       </c>
       <c r="D65" s="3">
-        <v>6.3</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="E65" s="2">
+        <v>5</v>
       </c>
       <c r="F65" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1757,18 +1953,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Enzo Lima</v>
+        <v>Rafael Carvalho</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D66" s="3">
-        <v>7.9</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+        <v>7.4</v>
+      </c>
+      <c r="E66" s="2">
+        <v>1</v>
       </c>
       <c r="F66" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G66" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1777,19 +1976,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Luiza Souza</v>
+        <v>Beatriz Pereira</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D67" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E67" s="2">
+        <v>5</v>
       </c>
       <c r="F67" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G67" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="68">
@@ -1797,19 +1999,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Matheus Gomes</v>
+        <v>Enzo Barbosa</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D68" s="3">
-        <v>8.3</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>6.4</v>
+      </c>
+      <c r="E68" s="2">
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G68" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="69">
@@ -1817,19 +2022,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Lorena Santos</v>
+        <v>Luiza Martins</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D69" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="E69" s="2">
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G69" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="70">
@@ -1837,19 +2045,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Benício Alves</v>
+        <v>Matheus Santos</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D70" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+        <v>8.5</v>
+      </c>
+      <c r="E70" s="2">
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G70" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="71">
@@ -1857,19 +2068,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Giovanna Barbosa</v>
+        <v>Lorena Almeida</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D71" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E71" s="2">
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G71" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="72">
@@ -1877,19 +2091,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Nicolas Soares</v>
+        <v>Benício Martins</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D72" s="3">
-        <v>8</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v>✓</v>
+        <v>7.7</v>
+      </c>
+      <c r="E72" s="2">
+        <v>3</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G72" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="73">
@@ -1897,19 +2114,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Mariana Fernandes</v>
+        <v>Giovanna Santos</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D73" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+        <v>7.6</v>
+      </c>
+      <c r="E73" s="2">
+        <v>5</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G73" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="74">
@@ -1917,18 +2137,21 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Gustavo Alves</v>
+        <v>Nicolas Costa</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D74" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+        <v>7.3</v>
+      </c>
+      <c r="E74" s="2">
+        <v>5</v>
       </c>
       <c r="F74" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1937,19 +2160,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Antonella Almeida</v>
+        <v>Mariana Oliveira</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D75" s="3">
-        <v>8</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="E75" s="2">
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G75" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="76">
@@ -1957,19 +2183,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Guilherme Barbosa</v>
+        <v>Gustavo Gomes</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D76" s="3">
-        <v>7.9</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>7.6</v>
+      </c>
+      <c r="E76" s="2">
+        <v>4</v>
       </c>
       <c r="F76" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G76" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="77">
@@ -1977,18 +2206,21 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Clara Barbosa</v>
+        <v>Antonella Lopes</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D77" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v>✓</v>
+        <v>7.9</v>
+      </c>
+      <c r="E77" s="2">
+        <v>3</v>
       </c>
       <c r="F77" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G77" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1997,19 +2229,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Miguel Soares</v>
+        <v>Guilherme Vieira</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D78" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>8.7</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
       </c>
       <c r="F78" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G78" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="79">
@@ -2017,19 +2252,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Helena Barbosa</v>
+        <v>Clara Gomes</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D79" s="3">
-        <v>8.8</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>6.9</v>
+      </c>
+      <c r="E79" s="2">
+        <v>1</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G79" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="80">
@@ -2037,19 +2275,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Arthur Lima</v>
+        <v>Joaquim Santos</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D80" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="E80" s="2">
+        <v>3</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G80" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="81">
@@ -2057,19 +2298,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Alice Alves</v>
+        <v>Helena Almeida</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D81" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>6.1</v>
+      </c>
+      <c r="E81" s="2">
+        <v>3</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G81" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="82">
@@ -2077,24 +2321,27 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Gael Almeida</v>
+        <v>Miguel Almeida</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D82" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>7.7</v>
+      </c>
+      <c r="E82" s="2">
+        <v>5</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2105,13 +2352,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2127,21 +2374,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="B1" s="2">
-        <v>77</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2149,4 +2396,84 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Critério</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Opções</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Gênero</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Média</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Número</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Nível de matemática</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Nível</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Apoio educacional</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Caixa de seleção</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Turma de origem</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
 </file>